--- a/Venous Data.xlsx
+++ b/Venous Data.xlsx
@@ -1,19 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F345973-FA74-49B7-A036-F894D19E7E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A45877A-32B2-4F76-8839-9CA8089F5728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{5B09B552-E1E7-4D5E-83AD-0BD0C565C1A0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{5B09B552-E1E7-4D5E-83AD-0BD0C565C1A0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Venous Data _ Sup" sheetId="2" r:id="rId1"/>
+    <sheet name="Venous Data _ Inf" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="26">
   <si>
     <t>Name</t>
   </si>
@@ -84,6 +87,36 @@
   </si>
   <si>
     <t>Not PR</t>
+  </si>
+  <si>
+    <t>Hepatic vein (64)</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>Inflow</t>
+  </si>
+  <si>
+    <t>Ref</t>
+  </si>
+  <si>
+    <t>Sup-Flow (ml/s)</t>
+  </si>
+  <si>
+    <t>Inf-Flow (ml/s)</t>
+  </si>
+  <si>
+    <t>2008_Ooue</t>
+  </si>
+  <si>
+    <t>2021_Takahashi</t>
+  </si>
+  <si>
+    <t>2021_Takahashi, 2022_Foor</t>
+  </si>
+  <si>
+    <t>2022_Foor</t>
   </si>
 </sst>
 </file>
@@ -616,6 +649,717 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE3328E-9C39-47E8-9767-EDCC58FB1C3F}">
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="26.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>28</v>
+      </c>
+      <c r="D2">
+        <f>D3+D4</f>
+        <v>25.5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <f>D3</f>
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <f>C5+C6</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <f>D4</f>
+        <v>16.5</v>
+      </c>
+      <c r="D4">
+        <f>C7+C8</f>
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D5">
+        <v>2.75</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D6">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D7">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>11.9</v>
+      </c>
+      <c r="D8">
+        <v>7.85</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <f>D6-C10</f>
+        <v>2.8499999999999996</v>
+      </c>
+      <c r="D9">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>4</v>
+      </c>
+      <c r="C10">
+        <v>1.75</v>
+      </c>
+      <c r="D10">
+        <f>C14</f>
+        <v>0.43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <f>D7-C12</f>
+        <v>2.8499999999999996</v>
+      </c>
+      <c r="D11">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>1.75</v>
+      </c>
+      <c r="D12">
+        <f>C16</f>
+        <v>0.43</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>2.11</v>
+      </c>
+      <c r="D13">
+        <f>C17+C18</f>
+        <v>1.29</v>
+      </c>
+      <c r="E13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>8</v>
+      </c>
+      <c r="C14">
+        <v>0.43</v>
+      </c>
+      <c r="D14">
+        <v>0.32</v>
+      </c>
+      <c r="E14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>9</v>
+      </c>
+      <c r="C15">
+        <v>2.31</v>
+      </c>
+      <c r="D15">
+        <f>C19+C20</f>
+        <v>1.29</v>
+      </c>
+      <c r="E15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>10</v>
+      </c>
+      <c r="C16">
+        <v>0.43</v>
+      </c>
+      <c r="D16">
+        <v>0.32</v>
+      </c>
+      <c r="E16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>11</v>
+      </c>
+      <c r="C17">
+        <v>0.6</v>
+      </c>
+      <c r="D17">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>11</v>
+      </c>
+      <c r="C18">
+        <v>0.69</v>
+      </c>
+      <c r="D18">
+        <v>0.32</v>
+      </c>
+      <c r="E18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>13</v>
+      </c>
+      <c r="C19">
+        <v>0.6</v>
+      </c>
+      <c r="D19">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>13</v>
+      </c>
+      <c r="C20">
+        <v>0.69</v>
+      </c>
+      <c r="D20">
+        <v>0.32</v>
+      </c>
+      <c r="E20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BA5D4AB-CEAB-460E-B24A-3C1986272137}">
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="26.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>28</v>
+      </c>
+      <c r="D2">
+        <f>D3+D4</f>
+        <v>25.5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <f>D3</f>
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <f>C5+C6</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <f>D4</f>
+        <v>16.5</v>
+      </c>
+      <c r="D4">
+        <f>C7+C8</f>
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D5">
+        <v>2.75</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D6">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D7">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>11.9</v>
+      </c>
+      <c r="D8">
+        <v>7.85</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <f>D6-C10</f>
+        <v>2.8499999999999996</v>
+      </c>
+      <c r="D9">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>4</v>
+      </c>
+      <c r="C10">
+        <v>1.75</v>
+      </c>
+      <c r="D10">
+        <f>C14</f>
+        <v>0.43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <f>D7-C12</f>
+        <v>2.8499999999999996</v>
+      </c>
+      <c r="D11">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>1.75</v>
+      </c>
+      <c r="D12">
+        <f>C16</f>
+        <v>0.43</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>2.11</v>
+      </c>
+      <c r="D13">
+        <f>C17+C18</f>
+        <v>1.29</v>
+      </c>
+      <c r="E13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>8</v>
+      </c>
+      <c r="C14">
+        <v>0.43</v>
+      </c>
+      <c r="D14">
+        <v>0.32</v>
+      </c>
+      <c r="E14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>9</v>
+      </c>
+      <c r="C15">
+        <v>2.31</v>
+      </c>
+      <c r="D15">
+        <f>C19+C20</f>
+        <v>1.29</v>
+      </c>
+      <c r="E15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>10</v>
+      </c>
+      <c r="C16">
+        <v>0.43</v>
+      </c>
+      <c r="D16">
+        <v>0.32</v>
+      </c>
+      <c r="E16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>11</v>
+      </c>
+      <c r="C17">
+        <v>0.6</v>
+      </c>
+      <c r="D17">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>11</v>
+      </c>
+      <c r="C18">
+        <v>0.69</v>
+      </c>
+      <c r="D18">
+        <v>0.32</v>
+      </c>
+      <c r="E18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>13</v>
+      </c>
+      <c r="C19">
+        <v>0.6</v>
+      </c>
+      <c r="D19">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>13</v>
+      </c>
+      <c r="C20">
+        <v>0.69</v>
+      </c>
+      <c r="D20">
+        <v>0.32</v>
+      </c>
+      <c r="E20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EEAAA27-B61C-4DD5-AD5C-FF5A56F8C17A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4A0BD93-4EA0-4FE3-932E-BDC36775F378}">
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -737,6 +1481,12 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>

--- a/Venous Data.xlsx
+++ b/Venous Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A45877A-32B2-4F76-8839-9CA8089F5728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7011392E-14FE-4F80-AFE4-2689C786F17E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{5B09B552-E1E7-4D5E-83AD-0BD0C565C1A0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="33">
   <si>
     <t>Name</t>
   </si>
@@ -117,6 +117,27 @@
   </si>
   <si>
     <t>2022_Foor</t>
+  </si>
+  <si>
+    <t>2002_Ogawa</t>
+  </si>
+  <si>
+    <t>2019_Husain-Syed</t>
+  </si>
+  <si>
+    <t>2004_Barakat</t>
+  </si>
+  <si>
+    <t>2024_Nie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024_Nie </t>
+  </si>
+  <si>
+    <t>linear interp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014_Muller, 2024_Nie </t>
   </si>
 </sst>
 </file>
@@ -132,12 +153,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -152,8 +179,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1001,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BA5D4AB-CEAB-460E-B24A-3C1986272137}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="15.7109375" customWidth="1"/>
@@ -1009,7 +1038,7 @@
     <col min="5" max="5" width="26.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>17</v>
       </c>
@@ -1026,22 +1055,19 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="D2">
-        <f>D3+D4</f>
-        <v>25.5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <f>C3+C4</f>
+        <v>45.300000000000004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1050,14 +1076,14 @@
       </c>
       <c r="C3">
         <f>D3</f>
-        <v>9</v>
+        <v>41.2</v>
       </c>
       <c r="D3">
         <f>C5+C6</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1065,15 +1091,16 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <f>D4</f>
-        <v>16.5</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="D4">
-        <f>C7+C8</f>
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1081,16 +1108,14 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>4.4000000000000004</v>
+        <v>37.1</v>
       </c>
       <c r="D5">
-        <v>2.75</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <f>C7+C8</f>
+        <v>37.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1098,183 +1123,178 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>4.5999999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="D6">
-        <v>4.5999999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="D7">
-        <v>4.5999999999999996</v>
+        <v>3</v>
+      </c>
+      <c r="C7" s="1">
+        <v>33</v>
+      </c>
+      <c r="D7" s="1">
+        <f>C8+C9</f>
+        <v>27.200000000000003</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>11.9</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="D8">
-        <v>7.85</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <f>D6-C10</f>
-        <v>2.8499999999999996</v>
+        <v>23.1</v>
       </c>
       <c r="D9">
-        <v>2.11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <f>C11+C10</f>
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10">
-        <v>1.75</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D10">
-        <f>C14</f>
-        <v>0.43</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11">
-        <v>5</v>
-      </c>
-      <c r="C11">
-        <f>D7-C12</f>
-        <v>2.8499999999999996</v>
-      </c>
-      <c r="D11">
-        <v>2.31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1">
+        <v>22</v>
+      </c>
+      <c r="D11" s="1">
+        <v>14.53</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="D12">
-        <f>C16</f>
-        <v>0.43</v>
+        <v>1.04</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C13">
-        <v>2.11</v>
+        <v>7.2649999999999997</v>
       </c>
       <c r="D13">
-        <f>C17+C18</f>
-        <v>1.29</v>
+        <v>6.7</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14">
-        <v>0.43</v>
-      </c>
-      <c r="D14">
-        <v>0.32</v>
-      </c>
+        <v>7.2649999999999997</v>
+      </c>
+      <c r="D14" s="2"/>
       <c r="E14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15">
-        <v>9</v>
-      </c>
-      <c r="C15">
-        <v>2.31</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15">
-        <f>C19+C20</f>
-        <v>1.29</v>
+        <v>6.7</v>
       </c>
       <c r="E15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C16">
-        <v>0.43</v>
+        <v>1.62</v>
       </c>
       <c r="D16">
-        <v>0.32</v>
-      </c>
-      <c r="E16" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1282,16 +1302,16 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17">
-        <v>0.6</v>
+        <v>5.08</v>
       </c>
       <c r="D17">
-        <v>0.28000000000000003</v>
+        <v>3.13</v>
       </c>
       <c r="E17" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1299,16 +1319,17 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C18">
-        <v>0.69</v>
+        <v>5.08</v>
       </c>
       <c r="D18">
-        <v>0.32</v>
+        <f>C20+C21</f>
+        <v>3.1300000000000003</v>
       </c>
       <c r="E18" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1319,13 +1340,10 @@
         <v>13</v>
       </c>
       <c r="C19">
-        <v>0.6</v>
+        <v>1.62</v>
       </c>
       <c r="D19">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="E19" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1333,16 +1351,67 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C20">
-        <v>0.69</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="D20">
-        <v>0.32</v>
+        <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>22</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>15</v>
+      </c>
+      <c r="C21">
+        <v>0.68</v>
+      </c>
+      <c r="D21">
+        <v>0.6</v>
+      </c>
+      <c r="E21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>16</v>
+      </c>
+      <c r="C22">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>16</v>
+      </c>
+      <c r="C23">
+        <v>0.68</v>
+      </c>
+      <c r="D23">
+        <v>0.6</v>
+      </c>
+      <c r="E23" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Venous Data.xlsx
+++ b/Venous Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7011392E-14FE-4F80-AFE4-2689C786F17E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0A6BEE-FC06-448A-8344-DDB89E9493FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{5B09B552-E1E7-4D5E-83AD-0BD0C565C1A0}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{5B09B552-E1E7-4D5E-83AD-0BD0C565C1A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Venous Data _ Sup" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="33">
   <si>
     <t>Name</t>
   </si>
@@ -181,8 +181,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1030,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BA5D4AB-CEAB-460E-B24A-3C1986272137}">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="15.7109375" customWidth="1"/>
@@ -1139,10 +1139,10 @@
       <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7">
         <v>33</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7">
         <f>C8+C9</f>
         <v>27.200000000000003</v>
       </c>
@@ -1206,10 +1206,10 @@
       <c r="B11">
         <v>7</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11">
         <v>22</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11">
         <v>14.53</v>
       </c>
       <c r="E11" t="s">
@@ -1243,8 +1243,8 @@
       <c r="C13">
         <v>7.2649999999999997</v>
       </c>
-      <c r="D13">
-        <v>6.7</v>
+      <c r="D13" s="1">
+        <v>6.82</v>
       </c>
       <c r="E13" t="s">
         <v>30</v>
@@ -1260,11 +1260,13 @@
       <c r="C14">
         <v>7.2649999999999997</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" s="2">
+        <v>6.7</v>
+      </c>
       <c r="E14" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="1" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1275,7 +1277,9 @@
       <c r="B15">
         <v>11</v>
       </c>
-      <c r="C15" s="2"/>
+      <c r="C15" s="1">
+        <v>6.82</v>
+      </c>
       <c r="D15">
         <v>6.7</v>
       </c>
@@ -1308,7 +1312,7 @@
         <v>5.08</v>
       </c>
       <c r="D17">
-        <v>3.13</v>
+        <v>5</v>
       </c>
       <c r="E17" t="s">
         <v>29</v>
@@ -1325,8 +1329,7 @@
         <v>5.08</v>
       </c>
       <c r="D18">
-        <f>C20+C21</f>
-        <v>3.1300000000000003</v>
+        <v>5</v>
       </c>
       <c r="E18" t="s">
         <v>29</v>
@@ -1354,13 +1357,11 @@
         <v>15</v>
       </c>
       <c r="C20">
-        <v>2.4500000000000002</v>
+        <v>3.6</v>
       </c>
       <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>26</v>
+        <f>C24+C25</f>
+        <v>3.1300000000000003</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1371,10 +1372,10 @@
         <v>15</v>
       </c>
       <c r="C21">
-        <v>0.68</v>
+        <v>1.4</v>
       </c>
       <c r="D21">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E21" t="s">
         <v>26</v>
@@ -1388,13 +1389,11 @@
         <v>16</v>
       </c>
       <c r="C22">
-        <v>2.4500000000000002</v>
+        <v>3.6</v>
       </c>
       <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22" t="s">
-        <v>26</v>
+        <f>C26+C27</f>
+        <v>3.1300000000000003</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1405,12 +1404,80 @@
         <v>16</v>
       </c>
       <c r="C23">
+        <v>1.4</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>18</v>
+      </c>
+      <c r="C24">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>18</v>
+      </c>
+      <c r="C25">
         <v>0.68</v>
       </c>
-      <c r="D23">
+      <c r="D25">
         <v>0.6</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E25" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>20</v>
+      </c>
+      <c r="C26">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>20</v>
+      </c>
+      <c r="C27">
+        <v>0.68</v>
+      </c>
+      <c r="D27">
+        <v>0.6</v>
+      </c>
+      <c r="E27" t="s">
         <v>26</v>
       </c>
     </row>

--- a/Venous Data.xlsx
+++ b/Venous Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0A6BEE-FC06-448A-8344-DDB89E9493FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1402584-B309-403F-A077-11445800A2F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{5B09B552-E1E7-4D5E-83AD-0BD0C565C1A0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5B09B552-E1E7-4D5E-83AD-0BD0C565C1A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Venous Data _ Sup" sheetId="2" r:id="rId1"/>
@@ -179,10 +179,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1260,7 +1259,7 @@
       <c r="C14">
         <v>7.2649999999999997</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14">
         <v>6.7</v>
       </c>
       <c r="E14" t="s">
